--- a/ejemplo_area de negocio.xlsx
+++ b/ejemplo_area de negocio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x16265\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38544D2B-5C39-4522-88F9-798DCCA1804A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F354A8C3-305F-4BCE-8B1E-B722A9DAC43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CFB41CF9-86DB-4151-B1F4-E32B055E30F5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="119">
   <si>
     <t>Banca</t>
   </si>
@@ -346,6 +346,60 @@
   </si>
   <si>
     <t>Nivel 4 = Personas</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>Banca Retail</t>
+  </si>
+  <si>
+    <t>Si son productos de Retail, lo podemos ubicar filtrando el nivel 4 de la jerarquía actual de productos igual a "Personas", entonces no importa el market segment, segmento comercial, ni el Tipo Gestión. El área de negocio será el segmento Retail. Pueden ser 3 valores. 2, 4 y 6.</t>
+  </si>
+  <si>
+    <t>Explicación</t>
+  </si>
+  <si>
+    <t>Si es un producto "Pagaré BPE" y la market segment es retail, inmobiliario, institucional, no importa el segmento retail, ni comercial, ni el tipo gestión. El area de negocio es negocio.</t>
+  </si>
+  <si>
+    <t>Si es un producto "Pagaré BPE" y la market segment es corporativo, no importa el segmento retail, ni comercial, pero si el tipo de gestión. Si es negocio, area de negocio corporativa, pero si es recupero va para negocio.</t>
+  </si>
+  <si>
+    <t>Si es un producto "Pagaré BPE" y la market segment es empresa,pero si es "g0" el segmento comercial y el tipo de gestión es "recupero" entonces el area de negocio es negocio, si el tipo gestión es "Negocio", entonces el area de negocio es Gestor Cero</t>
+  </si>
+  <si>
+    <t>Si es un producto "Pagaré BPE" y la market segment es empresa,pero si es "gran o mediana empresa" el segmento comercial y el tipo de gestión es "recupero" entonces el area de negocio es negocio, si el tipo gestión es "Negocio", entonces el area de negocio es empresa</t>
+  </si>
+  <si>
+    <t>Si es un producto "Pagaré BPE" y la market segment es Negocio, no importa el segmento retail, ni comercial, ni el tipo de gestión. Siempre es negocio</t>
+  </si>
+  <si>
+    <t>Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, ni el segmento comercial, si es market segment es Inmobiliario, no importa si es recupero/negocio, el area de negocio es Inmobiliaria</t>
+  </si>
+  <si>
+    <t>Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, ni el segmento comercial, si es market segment Institucional, no importa si es recupero/negocio, el area de negocio es Institucional</t>
+  </si>
+  <si>
+    <t>Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, ni el segmento comercial, si el market segment es  Institucional, y el tipo de gestion es corresponsalia, el area de negocio es corresponsalia</t>
+  </si>
+  <si>
+    <t>Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, ni el segmento comercial, si el market segmentl Corporativa, y el tipo de gestion puede ser recupero o negocio, el area de negocio es Corporativa</t>
+  </si>
+  <si>
+    <t>Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, si el market segment es empresa y si el segmento comercial es gran empresa y el tipo de gestion puede ser recupero o negocio, el area de negocio es gran empresa</t>
+  </si>
+  <si>
+    <t>Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, si el market segment es empresa y si el segmento comercial es mediana empresa y el tipo de gestion puede ser recupero o negocio, el area de negocio es mediana empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, si el market segment es empresa y si el segmento comercial es gestor cero y el tipo de gestion puede ser recupero o negocio, el area de negocio es gestor cero </t>
+  </si>
+  <si>
+    <t>Si es un producto del niverl 4 igual a empresa menos producto de pagaré bpe, no importa el segmento retail, si el market segment es negocio, el tipo de gestion puede ser recupero o negocio, el area de negocio es negocio</t>
+  </si>
+  <si>
+    <t>Si es un producto del nivel 3 personas, segmento retail no importa, market segment empresa, segmento comercial "g0" Y TIPO GESTIÓN ES RECUPERO, ENTONCES EL AREA DE NEGOCIO ES NEGOCIO.</t>
   </si>
 </sst>
 </file>
@@ -419,7 +473,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -531,11 +585,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -550,81 +613,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -634,6 +648,47 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,23 +1044,23 @@
       <c r="D7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="29" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C9" s="8"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +1069,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C10" s="8"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="2" t="s">
         <v>42</v>
       </c>
@@ -1023,7 +1078,7 @@
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="8"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="2" t="s">
         <v>4</v>
       </c>
@@ -1032,7 +1087,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="9"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1041,7 +1096,7 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="27" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -1052,7 +1107,7 @@
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C14" s="6"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1061,7 +1116,7 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="29" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -1072,8 +1127,8 @@
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="30"/>
+      <c r="D16" s="28" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -1081,15 +1136,15 @@
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="D17" s="12"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C18" s="9"/>
-      <c r="D18" s="12"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="2" t="s">
         <v>22</v>
       </c>
@@ -1221,214 +1276,203 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A1B15F-381B-43CE-B0A1-665D0DBC4059}">
-  <dimension ref="A2:H45"/>
+  <dimension ref="A2:I45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="44.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="43.140625" customWidth="1"/>
-    <col min="6" max="6" width="39.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="27"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="28"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="14"/>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="28"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
-      <c r="C5" s="26" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="28"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="14"/>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="28"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="14"/>
-      <c r="C7" s="26" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="28"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="29"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="28"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="22"/>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="28"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="19"/>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="29"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="28"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="14"/>
-      <c r="C13" s="26" t="s">
+      <c r="B13" s="23"/>
+      <c r="C13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="28"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="14"/>
-      <c r="C14" s="26" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="28"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="14"/>
-      <c r="C15" s="26" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="30"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="14"/>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="23"/>
+      <c r="C16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="29"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="28"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="19"/>
-      <c r="C18" s="15" t="s">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="26"/>
+      <c r="C18" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="28"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="16" t="s">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="29"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="20" t="s">
+      <c r="E19" s="16"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="5" t="s">
         <v>73</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -1437,485 +1481,553 @@
       <c r="E21" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="20" t="s">
+      <c r="H21" s="5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
+      <c r="I21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="25" t="s">
+      <c r="H22" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="B23" s="32" t="s">
+      <c r="I22" s="33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="34" t="s">
+      <c r="F23" s="34"/>
+      <c r="G23" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="36" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="B24" s="24" t="s">
+      <c r="I23" s="37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B24" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="31" t="s">
+      <c r="D24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="23"/>
-    </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B25" s="24" t="s">
+      <c r="H24" s="12"/>
+      <c r="I24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G25" s="24" t="s">
+      <c r="G25" s="13" t="s">
         <v>59</v>
       </c>
       <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B26" s="24" t="s">
+      <c r="I25" s="32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B27" s="24" t="s">
+      <c r="I26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="31" t="s">
+      <c r="E27" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B29" s="37" t="s">
+      <c r="I28" s="32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="19" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="37" t="s">
+      <c r="C29" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="38" t="s">
+      <c r="E29" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="G29" s="37" t="s">
+      <c r="G29" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H29" s="39"/>
-    </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B30" s="24" t="s">
+      <c r="H29" s="22"/>
+      <c r="I29" s="32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="24" t="s">
+      <c r="G30" s="13" t="s">
         <v>49</v>
       </c>
       <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B31" s="24" t="s">
+      <c r="I30" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B31" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="31" t="s">
+      <c r="E31" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G31" s="24" t="s">
+      <c r="G31" s="13" t="s">
         <v>49</v>
       </c>
       <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B32" s="24" t="s">
+      <c r="I31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B32" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="31" t="s">
+      <c r="E32" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G32" s="24" t="s">
+      <c r="G32" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B33" s="24" t="s">
+      <c r="I32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="9" t="s">
         <v>48</v>
       </c>
       <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B34" s="24" t="s">
+      <c r="I33" s="32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B34" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B35" s="24" t="s">
+      <c r="I34" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G35" s="24" t="s">
+      <c r="G35" s="13" t="s">
         <v>94</v>
       </c>
       <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B36" s="24" t="s">
+      <c r="I35" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="24" t="s">
+      <c r="D36" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="24" t="s">
+      <c r="G36" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B37" s="35" t="s">
+      <c r="I36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B37" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E37" s="35" t="s">
+      <c r="E37" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="35" t="s">
+      <c r="F37" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G37" s="35" t="s">
+      <c r="G37" s="13" t="s">
         <v>94</v>
       </c>
       <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B38" s="35" t="s">
+      <c r="I37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="35" t="s">
+      <c r="D38" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="35" t="s">
+      <c r="E38" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="35" t="s">
+      <c r="F38" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B39" s="24" t="s">
+      <c r="I38" s="33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B39" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="31" t="s">
+      <c r="E39" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G39" s="24" t="s">
+      <c r="G39" s="13" t="s">
         <v>89</v>
       </c>
       <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B40" s="24" t="s">
+      <c r="I39" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B40" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="31" t="s">
+      <c r="E40" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G40" s="24" t="s">
+      <c r="G40" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B41" s="24" t="s">
+      <c r="I40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B41" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F41" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G41" s="24" t="s">
+      <c r="G41" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B42" s="24" t="s">
+      <c r="I41" s="32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B42" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G42" s="24" t="s">
+      <c r="G42" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
+      <c r="I42" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
       <c r="H45" s="1"/>
     </row>
   </sheetData>
